--- a/artfynd/A 16004-2025 artfynd.xlsx
+++ b/artfynd/A 16004-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123842779</v>
+        <v>123842288</v>
       </c>
       <c r="B2" t="n">
         <v>98502</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -719,17 +719,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Knärot4, Sm</t>
+          <t>Knärot2, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568160</v>
+        <v>568186</v>
       </c>
       <c r="R2" t="n">
-        <v>6398949</v>
+        <v>6398957</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123842288</v>
+        <v>123842779</v>
       </c>
       <c r="B3" t="n">
         <v>98502</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -830,17 +830,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Knärot2, Sm</t>
+          <t>Knärot4, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568186</v>
+        <v>568160</v>
       </c>
       <c r="R3" t="n">
-        <v>6398957</v>
+        <v>6398949</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1006,6 +1006,907 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123875073</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98502</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>568169</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6398913</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123875158</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98502</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>568173</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6398964</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123875213</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98502</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>568121</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6398922</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123875253</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90424</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2008</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fyrflikig jordstjärna</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Geastrum quadrifidum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>568147</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6398938</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123875178</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57643</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>568147</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6398938</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123875271</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57506</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>568147</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6398938</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123875103</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57506</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>568178</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6398985</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Bearbetat stubbe</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123875130</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98502</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>568185</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6398991</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16004-2025 artfynd.xlsx
+++ b/artfynd/A 16004-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123842288</v>
+        <v>123842561</v>
       </c>
       <c r="B2" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -719,17 +719,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Knärot2, Sm</t>
+          <t>Knärot3, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568186</v>
+        <v>568178</v>
       </c>
       <c r="R2" t="n">
-        <v>6398957</v>
+        <v>6398997</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123842779</v>
+        <v>123842288</v>
       </c>
       <c r="B3" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -830,17 +830,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Knärot4, Sm</t>
+          <t>Knärot2, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568160</v>
+        <v>568186</v>
       </c>
       <c r="R3" t="n">
-        <v>6398949</v>
+        <v>6398957</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,17 +890,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123842561</v>
+        <v>123842779</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -941,14 +941,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Knärot3, Sm</t>
+          <t>Knärot4, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568178</v>
+        <v>568160</v>
       </c>
       <c r="R4" t="n">
-        <v>6398997</v>
+        <v>6398949</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123875073</v>
+        <v>123875271</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>57507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,35 +1020,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1056,13 +1060,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568169</v>
+        <v>568147</v>
       </c>
       <c r="R5" t="n">
-        <v>6398913</v>
+        <v>6398938</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,7 +1104,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1119,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123875158</v>
+        <v>123875253</v>
       </c>
       <c r="B6" t="n">
-        <v>98502</v>
+        <v>90426</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,35 +1134,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2008</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1167,13 +1173,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568173</v>
+        <v>568147</v>
       </c>
       <c r="R6" t="n">
-        <v>6398964</v>
+        <v>6398938</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1233,7 +1239,7 @@
         <v>123875213</v>
       </c>
       <c r="B7" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1341,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123875253</v>
+        <v>123875103</v>
       </c>
       <c r="B8" t="n">
-        <v>90424</v>
+        <v>57507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,34 +1363,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2008</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1392,13 +1395,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568147</v>
+        <v>568178</v>
       </c>
       <c r="R8" t="n">
-        <v>6398938</v>
+        <v>6398985</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1430,13 +1433,17 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Bearbetat stubbe</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1458,7 +1465,7 @@
         <v>123875178</v>
       </c>
       <c r="B9" t="n">
-        <v>57643</v>
+        <v>57644</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1569,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123875271</v>
+        <v>123875073</v>
       </c>
       <c r="B10" t="n">
-        <v>57506</v>
+        <v>98504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1581,39 +1588,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1621,13 +1624,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568147</v>
+        <v>568169</v>
       </c>
       <c r="R10" t="n">
-        <v>6398938</v>
+        <v>6398913</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1665,6 +1668,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1683,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123875103</v>
+        <v>123875130</v>
       </c>
       <c r="B11" t="n">
-        <v>57506</v>
+        <v>98504</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,35 +1699,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1731,10 +1735,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568178</v>
+        <v>568185</v>
       </c>
       <c r="R11" t="n">
-        <v>6398985</v>
+        <v>6398991</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1769,17 +1773,13 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Bearbetat stubbe</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1798,10 +1798,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123875130</v>
+        <v>123875158</v>
       </c>
       <c r="B12" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568185</v>
+        <v>568173</v>
       </c>
       <c r="R12" t="n">
-        <v>6398991</v>
+        <v>6398964</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 16004-2025 artfynd.xlsx
+++ b/artfynd/A 16004-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1907,6 +1907,5119 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123954103</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>568389</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6399101</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123949558</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>knärot17, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>568320</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6399077</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123954151</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57507</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>568376</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6399112</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123953836</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>568294</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6399059</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123949240</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>knärot6, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>568285</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6399024</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123953317</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>568247</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6399025</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123949609</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>knärot21, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>568313</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6399119</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>123953575</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>568284</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6399026</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>123953509</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>568275</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6399010</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>123949415</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>knärot12, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>568329</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6399041</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>123954184</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57507</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>568372</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6399087</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>123953289</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>568244</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6399023</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>123953185</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>568156</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6398944</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>123949249</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>knärot7, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>568291</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6399043</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>123949566</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>knärot18, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>568308</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6399081</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>123949298</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>knärot10, Sm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>568243</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6399034</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>123949221</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Knärot5, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>568277</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6399002</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>123953122</v>
+      </c>
+      <c r="B30" t="n">
+        <v>90426</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2008</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Fyrflikig jordstjärna</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Geastrum quadrifidum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>568149</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6398945</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>123953590</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>568287</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6399029</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>123953467</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>568277</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6399026</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>123953794</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>568305</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6399047</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>123953665</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>568251</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6399046</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>123954009</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>568399</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6399091</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>123949545</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>knärot16, Sm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>568267</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6399069</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>123953357</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>568247</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6399016</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>123949584</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>knärot20, Sm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>568393</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6399083</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>123949577</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>knärot19, Sm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>568383</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6399086</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>123953963</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>568310</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6399096</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>123953533</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>568291</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6398999</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>123953648</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57507</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>568268</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6399043</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>123949261</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>knärot8, Sm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>568271</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6399036</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>123953735</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>568269</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6399049</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>123953913</v>
+      </c>
+      <c r="B45" t="n">
+        <v>105520</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>568321</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6399110</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>123953616</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>568263</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6399041</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>123953227</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>568237</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6399031</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>123953876</v>
+      </c>
+      <c r="B48" t="n">
+        <v>90990</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>568313</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6399116</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>123953938</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>568321</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6399110</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>123953559</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>568271</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6399014</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>123953814</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>568298</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6399059</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>123953775</v>
+      </c>
+      <c r="B52" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>568273</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6399048</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>123949592</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>knärot21, Sm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>568397</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6399096</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>123953683</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>568248</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6399053</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>123953988</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>568342</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6399127</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>123949273</v>
+      </c>
+      <c r="B56" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>knärot9, Sm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>568260</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6399040</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>123949397</v>
+      </c>
+      <c r="B57" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>knärot11, Sm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>568292</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6399045</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>123954300</v>
+      </c>
+      <c r="B58" t="n">
+        <v>56700</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>A 16004, Sm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>568340</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6399053</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Flera fjödrar ovh dun.</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16004-2025 artfynd.xlsx
+++ b/artfynd/A 16004-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2907,10 +2907,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123949415</v>
+        <v>123954184</v>
       </c>
       <c r="B22" t="n">
-        <v>98504</v>
+        <v>57507</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2919,49 +2919,49 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>knärot12, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>568329</v>
+        <v>568372</v>
       </c>
       <c r="R22" t="n">
-        <v>6399041</v>
+        <v>6399087</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2999,29 +2999,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123954184</v>
+        <v>123953289</v>
       </c>
       <c r="B23" t="n">
-        <v>57507</v>
+        <v>98504</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3030,35 +3029,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3066,10 +3065,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>568372</v>
+        <v>568244</v>
       </c>
       <c r="R23" t="n">
-        <v>6399087</v>
+        <v>6399023</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3110,6 +3109,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3128,7 +3128,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123953289</v>
+        <v>123949415</v>
       </c>
       <c r="B24" t="n">
         <v>98504</v>
@@ -3161,28 +3161,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot12, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>568244</v>
+        <v>568329</v>
       </c>
       <c r="R24" t="n">
-        <v>6399023</v>
+        <v>6399041</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3227,12 +3227,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123953357</v>
+        <v>123949584</v>
       </c>
       <c r="B37" t="n">
         <v>98504</v>
@@ -4607,28 +4607,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot20, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>568247</v>
+        <v>568393</v>
       </c>
       <c r="R37" t="n">
-        <v>6399016</v>
+        <v>6399083</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4673,19 +4673,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123949584</v>
+        <v>123949577</v>
       </c>
       <c r="B38" t="n">
         <v>98504</v>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -4729,14 +4729,14 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>knärot20, Sm</t>
+          <t>knärot19, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>568393</v>
+        <v>568383</v>
       </c>
       <c r="R38" t="n">
-        <v>6399083</v>
+        <v>6399086</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4796,7 +4796,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123949577</v>
+        <v>123953357</v>
       </c>
       <c r="B39" t="n">
         <v>98504</v>
@@ -4829,28 +4829,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>knärot19, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>568383</v>
+        <v>568247</v>
       </c>
       <c r="R39" t="n">
-        <v>6399086</v>
+        <v>6399016</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4895,12 +4895,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5129,10 +5129,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123953648</v>
+        <v>123949261</v>
       </c>
       <c r="B42" t="n">
-        <v>57507</v>
+        <v>98504</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5141,49 +5141,49 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot8, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>568268</v>
+        <v>568271</v>
       </c>
       <c r="R42" t="n">
-        <v>6399043</v>
+        <v>6399036</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5221,28 +5221,29 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123949261</v>
+        <v>123953648</v>
       </c>
       <c r="B43" t="n">
-        <v>98504</v>
+        <v>57507</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5251,49 +5252,49 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>knärot8, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>568271</v>
+        <v>568268</v>
       </c>
       <c r="R43" t="n">
-        <v>6399036</v>
+        <v>6399043</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5331,19 +5332,18 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -7020,6 +7020,235 @@
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>123978490</v>
+      </c>
+      <c r="B59" t="n">
+        <v>97369</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>568355</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6399066</v>
+      </c>
+      <c r="S59" t="n">
+        <v>25</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>123978510</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57861</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>568326</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6399091</v>
+      </c>
+      <c r="S60" t="n">
+        <v>50</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16004-2025 artfynd.xlsx
+++ b/artfynd/A 16004-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AY61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123842561</v>
+        <v>123842779</v>
       </c>
       <c r="B2" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -719,14 +719,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Knärot3, Sm</t>
+          <t>Knärot4, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568178</v>
+        <v>568160</v>
       </c>
       <c r="R2" t="n">
-        <v>6398997</v>
+        <v>6398949</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123842288</v>
+        <v>123842053</v>
       </c>
       <c r="B3" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -830,17 +830,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Knärot2, Sm</t>
+          <t>Knärot1, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568186</v>
+        <v>568157</v>
       </c>
       <c r="R3" t="n">
-        <v>6398957</v>
+        <v>6398918</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,17 +890,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123842779</v>
+        <v>123842561</v>
       </c>
       <c r="B4" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -941,14 +941,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Knärot4, Sm</t>
+          <t>Knärot3, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568160</v>
+        <v>568178</v>
       </c>
       <c r="R4" t="n">
-        <v>6398949</v>
+        <v>6398997</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123875271</v>
+        <v>123842288</v>
       </c>
       <c r="B5" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,50 +1020,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>Knärot2, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568147</v>
+        <v>568186</v>
       </c>
       <c r="R5" t="n">
-        <v>6398938</v>
+        <v>6398957</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1104,28 +1100,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123875253</v>
+        <v>123875130</v>
       </c>
       <c r="B6" t="n">
-        <v>90426</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,38 +1131,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2008</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1173,13 +1167,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568147</v>
+        <v>568185</v>
       </c>
       <c r="R6" t="n">
-        <v>6398938</v>
+        <v>6398991</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1236,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123875213</v>
+        <v>123875253</v>
       </c>
       <c r="B7" t="n">
-        <v>98504</v>
+        <v>90426</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,35 +1242,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>2008</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1284,13 +1281,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568121</v>
+        <v>568147</v>
       </c>
       <c r="R7" t="n">
-        <v>6398922</v>
+        <v>6398938</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1347,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123875103</v>
+        <v>123875178</v>
       </c>
       <c r="B8" t="n">
-        <v>57507</v>
+        <v>57644</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,29 +1360,33 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1395,13 +1396,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568178</v>
+        <v>568147</v>
       </c>
       <c r="R8" t="n">
-        <v>6398985</v>
+        <v>6398938</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1431,11 +1432,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Bearbetat stubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123875178</v>
+        <v>123875158</v>
       </c>
       <c r="B9" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1474,39 +1470,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1514,13 +1506,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568147</v>
+        <v>568173</v>
       </c>
       <c r="R9" t="n">
-        <v>6398938</v>
+        <v>6398964</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1558,6 +1550,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1579,7 +1572,7 @@
         <v>123875073</v>
       </c>
       <c r="B10" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1687,10 +1680,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123875130</v>
+        <v>123875103</v>
       </c>
       <c r="B11" t="n">
-        <v>98504</v>
+        <v>57507</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,35 +1692,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1735,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568185</v>
+        <v>568178</v>
       </c>
       <c r="R11" t="n">
-        <v>6398991</v>
+        <v>6398985</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1773,13 +1766,17 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Bearbetat stubbe</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1798,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123875158</v>
+        <v>123875213</v>
       </c>
       <c r="B12" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,10 +1843,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568173</v>
+        <v>568121</v>
       </c>
       <c r="R12" t="n">
-        <v>6398964</v>
+        <v>6398922</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1909,10 +1906,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123954103</v>
+        <v>123875271</v>
       </c>
       <c r="B13" t="n">
-        <v>98504</v>
+        <v>57507</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1921,35 +1918,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1957,13 +1958,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>568389</v>
+        <v>568147</v>
       </c>
       <c r="R13" t="n">
-        <v>6399101</v>
+        <v>6398938</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1987,12 +1988,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2001,7 +2002,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2020,10 +2020,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123949558</v>
+        <v>123953814</v>
       </c>
       <c r="B14" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2053,28 +2053,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>knärot17, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>568320</v>
+        <v>568298</v>
       </c>
       <c r="R14" t="n">
-        <v>6399077</v>
+        <v>6399059</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2119,22 +2119,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123954151</v>
+        <v>123949240</v>
       </c>
       <c r="B15" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2143,49 +2143,49 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot6, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>568376</v>
+        <v>568285</v>
       </c>
       <c r="R15" t="n">
-        <v>6399112</v>
+        <v>6399024</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2223,28 +2223,29 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123953836</v>
+        <v>123954009</v>
       </c>
       <c r="B16" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2289,10 +2290,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>568294</v>
+        <v>568399</v>
       </c>
       <c r="R16" t="n">
-        <v>6399059</v>
+        <v>6399091</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2345,17 +2346,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123949240</v>
+        <v>123953938</v>
       </c>
       <c r="B17" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2385,28 +2386,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>knärot6, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>568285</v>
+        <v>568321</v>
       </c>
       <c r="R17" t="n">
-        <v>6399024</v>
+        <v>6399110</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2451,22 +2452,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123953317</v>
+        <v>123949273</v>
       </c>
       <c r="B18" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2496,28 +2497,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot9, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>568247</v>
+        <v>568260</v>
       </c>
       <c r="R18" t="n">
-        <v>6399025</v>
+        <v>6399040</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2562,22 +2563,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123949609</v>
+        <v>123953317</v>
       </c>
       <c r="B19" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2607,28 +2608,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>knärot21, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>568313</v>
+        <v>568247</v>
       </c>
       <c r="R19" t="n">
-        <v>6399119</v>
+        <v>6399025</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2673,22 +2674,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123953575</v>
+        <v>123953357</v>
       </c>
       <c r="B20" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2733,10 +2734,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>568284</v>
+        <v>568247</v>
       </c>
       <c r="R20" t="n">
-        <v>6399026</v>
+        <v>6399016</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2796,10 +2797,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123953509</v>
+        <v>123953575</v>
       </c>
       <c r="B21" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2844,10 +2845,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>568275</v>
+        <v>568284</v>
       </c>
       <c r="R21" t="n">
-        <v>6399010</v>
+        <v>6399026</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2907,10 +2908,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123954184</v>
+        <v>123953289</v>
       </c>
       <c r="B22" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2919,35 +2920,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2955,10 +2956,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>568372</v>
+        <v>568244</v>
       </c>
       <c r="R22" t="n">
-        <v>6399087</v>
+        <v>6399023</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2999,6 +3000,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3017,10 +3019,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123953289</v>
+        <v>123949592</v>
       </c>
       <c r="B23" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3050,28 +3052,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot21, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>568244</v>
+        <v>568397</v>
       </c>
       <c r="R23" t="n">
-        <v>6399023</v>
+        <v>6399096</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3116,22 +3118,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123949415</v>
+        <v>123953559</v>
       </c>
       <c r="B24" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3161,28 +3163,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>knärot12, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>568329</v>
+        <v>568271</v>
       </c>
       <c r="R24" t="n">
-        <v>6399041</v>
+        <v>6399014</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3227,22 +3229,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123953185</v>
+        <v>123954151</v>
       </c>
       <c r="B25" t="n">
-        <v>98504</v>
+        <v>57507</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3251,35 +3253,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3287,10 +3289,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>568156</v>
+        <v>568376</v>
       </c>
       <c r="R25" t="n">
-        <v>6398944</v>
+        <v>6399112</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3331,7 +3333,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3350,10 +3351,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123949249</v>
+        <v>123954103</v>
       </c>
       <c r="B26" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3383,28 +3384,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>knärot7, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>568291</v>
+        <v>568389</v>
       </c>
       <c r="R26" t="n">
-        <v>6399043</v>
+        <v>6399101</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3449,7 +3450,7 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
@@ -3461,10 +3462,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123949566</v>
+        <v>123953913</v>
       </c>
       <c r="B27" t="n">
-        <v>98504</v>
+        <v>105095</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3473,49 +3474,49 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>knärot18, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>568308</v>
+        <v>568321</v>
       </c>
       <c r="R27" t="n">
-        <v>6399081</v>
+        <v>6399110</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3560,22 +3561,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123949298</v>
+        <v>123949584</v>
       </c>
       <c r="B28" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3607,7 +3608,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -3616,14 +3617,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>knärot10, Sm</t>
+          <t>knärot20, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>568243</v>
+        <v>568393</v>
       </c>
       <c r="R28" t="n">
-        <v>6399034</v>
+        <v>6399083</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3683,10 +3684,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123949221</v>
+        <v>123949397</v>
       </c>
       <c r="B29" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3718,7 +3719,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -3727,14 +3728,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Knärot5, Sm</t>
+          <t>knärot11, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>568277</v>
+        <v>568292</v>
       </c>
       <c r="R29" t="n">
-        <v>6399002</v>
+        <v>6399045</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3794,10 +3795,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123953122</v>
+        <v>123949609</v>
       </c>
       <c r="B30" t="n">
-        <v>90426</v>
+        <v>98079</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3806,25 +3807,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2008</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3832,26 +3833,23 @@
           <t>3</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot21, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>568149</v>
+        <v>568313</v>
       </c>
       <c r="R30" t="n">
-        <v>6398945</v>
+        <v>6399119</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3896,12 +3894,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3911,7 +3909,7 @@
         <v>123953590</v>
       </c>
       <c r="B31" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4019,10 +4017,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123953467</v>
+        <v>123953616</v>
       </c>
       <c r="B32" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4067,10 +4065,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>568277</v>
+        <v>568263</v>
       </c>
       <c r="R32" t="n">
-        <v>6399026</v>
+        <v>6399041</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4130,10 +4128,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123953794</v>
+        <v>123953122</v>
       </c>
       <c r="B33" t="n">
-        <v>98504</v>
+        <v>90426</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4142,35 +4140,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>2008</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4178,10 +4179,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>568305</v>
+        <v>568149</v>
       </c>
       <c r="R33" t="n">
-        <v>6399047</v>
+        <v>6398945</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4241,10 +4242,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123953665</v>
+        <v>123953533</v>
       </c>
       <c r="B34" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4289,10 +4290,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>568251</v>
+        <v>568291</v>
       </c>
       <c r="R34" t="n">
-        <v>6399046</v>
+        <v>6398999</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4352,10 +4353,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123954009</v>
+        <v>123953836</v>
       </c>
       <c r="B35" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4400,10 +4401,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>568399</v>
+        <v>568294</v>
       </c>
       <c r="R35" t="n">
-        <v>6399091</v>
+        <v>6399059</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4466,7 +4467,7 @@
         <v>123949545</v>
       </c>
       <c r="B36" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4574,10 +4575,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123949584</v>
+        <v>123949221</v>
       </c>
       <c r="B37" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4609,7 +4610,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
@@ -4618,14 +4619,14 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>knärot20, Sm</t>
+          <t>Knärot5, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>568393</v>
+        <v>568277</v>
       </c>
       <c r="R37" t="n">
-        <v>6399083</v>
+        <v>6399002</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4685,10 +4686,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123949577</v>
+        <v>123953876</v>
       </c>
       <c r="B38" t="n">
-        <v>98504</v>
+        <v>90990</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4697,49 +4698,52 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>knärot19, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>568383</v>
+        <v>568313</v>
       </c>
       <c r="R38" t="n">
-        <v>6399086</v>
+        <v>6399116</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4784,22 +4788,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123953357</v>
+        <v>123953963</v>
       </c>
       <c r="B39" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4844,10 +4848,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>568247</v>
+        <v>568310</v>
       </c>
       <c r="R39" t="n">
-        <v>6399016</v>
+        <v>6399096</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4907,10 +4911,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123953963</v>
+        <v>123953794</v>
       </c>
       <c r="B40" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4955,10 +4959,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>568310</v>
+        <v>568305</v>
       </c>
       <c r="R40" t="n">
-        <v>6399096</v>
+        <v>6399047</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5018,10 +5022,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123953533</v>
+        <v>123949261</v>
       </c>
       <c r="B41" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5051,28 +5055,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot8, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>568291</v>
+        <v>568271</v>
       </c>
       <c r="R41" t="n">
-        <v>6398999</v>
+        <v>6399036</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5117,22 +5121,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123949261</v>
+        <v>123949298</v>
       </c>
       <c r="B42" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5173,14 +5177,14 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>knärot8, Sm</t>
+          <t>knärot10, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>568271</v>
+        <v>568243</v>
       </c>
       <c r="R42" t="n">
-        <v>6399036</v>
+        <v>6399034</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5240,10 +5244,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123953648</v>
+        <v>123953775</v>
       </c>
       <c r="B43" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5252,35 +5256,35 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5288,13 +5292,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>568268</v>
+        <v>568273</v>
       </c>
       <c r="R43" t="n">
-        <v>6399043</v>
+        <v>6399048</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5332,6 +5336,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5350,10 +5355,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123953735</v>
+        <v>123953988</v>
       </c>
       <c r="B44" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5398,10 +5403,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>568269</v>
+        <v>568342</v>
       </c>
       <c r="R44" t="n">
-        <v>6399049</v>
+        <v>6399127</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5461,10 +5466,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123953913</v>
+        <v>123949558</v>
       </c>
       <c r="B45" t="n">
-        <v>105520</v>
+        <v>98079</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5473,49 +5478,49 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot17, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>568321</v>
+        <v>568320</v>
       </c>
       <c r="R45" t="n">
-        <v>6399110</v>
+        <v>6399077</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5560,22 +5565,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123953616</v>
+        <v>123949415</v>
       </c>
       <c r="B46" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5605,28 +5610,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot12, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>568263</v>
+        <v>568329</v>
       </c>
       <c r="R46" t="n">
         <v>6399041</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5671,22 +5676,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123953227</v>
+        <v>123954184</v>
       </c>
       <c r="B47" t="n">
-        <v>98504</v>
+        <v>57507</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5695,35 +5700,35 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5731,10 +5736,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>568237</v>
+        <v>568372</v>
       </c>
       <c r="R47" t="n">
-        <v>6399031</v>
+        <v>6399087</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5775,7 +5780,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5794,10 +5798,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123953876</v>
+        <v>123953185</v>
       </c>
       <c r="B48" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5806,38 +5810,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5845,10 +5846,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>568313</v>
+        <v>568156</v>
       </c>
       <c r="R48" t="n">
-        <v>6399116</v>
+        <v>6398944</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5908,10 +5909,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123953938</v>
+        <v>123953735</v>
       </c>
       <c r="B49" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5956,10 +5957,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>568321</v>
+        <v>568269</v>
       </c>
       <c r="R49" t="n">
-        <v>6399110</v>
+        <v>6399049</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6019,10 +6020,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123953559</v>
+        <v>123954300</v>
       </c>
       <c r="B50" t="n">
-        <v>98504</v>
+        <v>56700</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6031,46 +6032,50 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>A 16004, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>568271</v>
+        <v>568340</v>
       </c>
       <c r="R50" t="n">
-        <v>6399014</v>
+        <v>6399053</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6105,13 +6110,17 @@
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Flera fjödrar ovh dun.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6130,10 +6139,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123953814</v>
+        <v>123949249</v>
       </c>
       <c r="B51" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6163,28 +6172,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot7, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>568298</v>
+        <v>568291</v>
       </c>
       <c r="R51" t="n">
-        <v>6399059</v>
+        <v>6399043</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6229,22 +6238,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123953775</v>
+        <v>123953683</v>
       </c>
       <c r="B52" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6275,11 +6284,7 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
@@ -6289,10 +6294,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>568273</v>
+        <v>568248</v>
       </c>
       <c r="R52" t="n">
-        <v>6399048</v>
+        <v>6399053</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6352,10 +6357,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123949592</v>
+        <v>123953665</v>
       </c>
       <c r="B53" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6385,28 +6390,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>knärot21, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>568397</v>
+        <v>568251</v>
       </c>
       <c r="R53" t="n">
-        <v>6399096</v>
+        <v>6399046</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6451,22 +6456,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123953683</v>
+        <v>123953509</v>
       </c>
       <c r="B54" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6497,7 +6502,11 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
@@ -6507,10 +6516,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>568248</v>
+        <v>568275</v>
       </c>
       <c r="R54" t="n">
-        <v>6399053</v>
+        <v>6399010</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6570,10 +6579,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123953988</v>
+        <v>123953467</v>
       </c>
       <c r="B55" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6618,10 +6627,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>568342</v>
+        <v>568277</v>
       </c>
       <c r="R55" t="n">
-        <v>6399127</v>
+        <v>6399026</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6674,17 +6683,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123949273</v>
+        <v>123949577</v>
       </c>
       <c r="B56" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6716,7 +6725,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
@@ -6725,14 +6734,14 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>knärot9, Sm</t>
+          <t>knärot19, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>568260</v>
+        <v>568383</v>
       </c>
       <c r="R56" t="n">
-        <v>6399040</v>
+        <v>6399086</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6792,10 +6801,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123949397</v>
+        <v>123953227</v>
       </c>
       <c r="B57" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6825,28 +6834,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>knärot11, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>568292</v>
+        <v>568237</v>
       </c>
       <c r="R57" t="n">
-        <v>6399045</v>
+        <v>6399031</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6891,22 +6900,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123954300</v>
+        <v>123949566</v>
       </c>
       <c r="B58" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6915,53 +6924,49 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>funnen död</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>A 16004, Sm</t>
+          <t>knärot18, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>568340</v>
+        <v>568308</v>
       </c>
       <c r="R58" t="n">
-        <v>6399053</v>
+        <v>6399081</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6993,39 +6998,35 @@
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Flera fjödrar ovh dun.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123978490</v>
+        <v>123953648</v>
       </c>
       <c r="B59" t="n">
-        <v>97369</v>
+        <v>57507</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7034,39 +7035,35 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7074,10 +7071,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>568355</v>
+        <v>568268</v>
       </c>
       <c r="R59" t="n">
-        <v>6399066</v>
+        <v>6399043</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7118,7 +7115,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7249,6 +7245,121 @@
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>123978490</v>
+      </c>
+      <c r="B61" t="n">
+        <v>96957</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>A 16004, Ytterbo, Sm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>568355</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6399066</v>
+      </c>
+      <c r="S61" t="n">
+        <v>25</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16004-2025 artfynd.xlsx
+++ b/artfynd/A 16004-2025 artfynd.xlsx
@@ -1344,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123875178</v>
+        <v>123875158</v>
       </c>
       <c r="B8" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,39 +1356,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1396,13 +1392,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568147</v>
+        <v>568173</v>
       </c>
       <c r="R8" t="n">
-        <v>6398938</v>
+        <v>6398964</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,6 +1436,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1458,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123875158</v>
+        <v>123875178</v>
       </c>
       <c r="B9" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,35 +1467,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1506,13 +1507,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568173</v>
+        <v>568147</v>
       </c>
       <c r="R9" t="n">
-        <v>6398964</v>
+        <v>6398938</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1550,7 +1551,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -2353,7 +2353,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123953938</v>
+        <v>123949273</v>
       </c>
       <c r="B17" t="n">
         <v>98079</v>
@@ -2386,28 +2386,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot9, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>568321</v>
+        <v>568260</v>
       </c>
       <c r="R17" t="n">
-        <v>6399110</v>
+        <v>6399040</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2452,19 +2452,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123949273</v>
+        <v>123953938</v>
       </c>
       <c r="B18" t="n">
         <v>98079</v>
@@ -2497,28 +2497,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>knärot9, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>568260</v>
+        <v>568321</v>
       </c>
       <c r="R18" t="n">
-        <v>6399040</v>
+        <v>6399110</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2563,12 +2563,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3684,7 +3684,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123949397</v>
+        <v>123953590</v>
       </c>
       <c r="B29" t="n">
         <v>98079</v>
@@ -3717,28 +3717,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>knärot11, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>568292</v>
+        <v>568287</v>
       </c>
       <c r="R29" t="n">
-        <v>6399045</v>
+        <v>6399029</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3783,19 +3783,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123949609</v>
+        <v>123953616</v>
       </c>
       <c r="B30" t="n">
         <v>98079</v>
@@ -3828,28 +3828,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>knärot21, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>568313</v>
+        <v>568263</v>
       </c>
       <c r="R30" t="n">
-        <v>6399119</v>
+        <v>6399041</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3894,19 +3894,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123953590</v>
+        <v>123949397</v>
       </c>
       <c r="B31" t="n">
         <v>98079</v>
@@ -3939,28 +3939,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot11, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>568287</v>
+        <v>568292</v>
       </c>
       <c r="R31" t="n">
-        <v>6399029</v>
+        <v>6399045</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4005,19 +4005,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123953616</v>
+        <v>123949609</v>
       </c>
       <c r="B32" t="n">
         <v>98079</v>
@@ -4050,28 +4050,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot21, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>568263</v>
+        <v>568313</v>
       </c>
       <c r="R32" t="n">
-        <v>6399041</v>
+        <v>6399119</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4116,22 +4116,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123953122</v>
+        <v>123953533</v>
       </c>
       <c r="B33" t="n">
-        <v>90426</v>
+        <v>98079</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4140,38 +4140,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2008</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4179,10 +4176,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>568149</v>
+        <v>568291</v>
       </c>
       <c r="R33" t="n">
-        <v>6398945</v>
+        <v>6398999</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4242,7 +4239,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123953533</v>
+        <v>123953836</v>
       </c>
       <c r="B34" t="n">
         <v>98079</v>
@@ -4290,10 +4287,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>568291</v>
+        <v>568294</v>
       </c>
       <c r="R34" t="n">
-        <v>6398999</v>
+        <v>6399059</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4353,7 +4350,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123953836</v>
+        <v>123949545</v>
       </c>
       <c r="B35" t="n">
         <v>98079</v>
@@ -4386,28 +4383,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot16, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>568294</v>
+        <v>568267</v>
       </c>
       <c r="R35" t="n">
-        <v>6399059</v>
+        <v>6399069</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4452,22 +4449,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123949545</v>
+        <v>123953122</v>
       </c>
       <c r="B36" t="n">
-        <v>98079</v>
+        <v>90426</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4476,49 +4473,52 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>2008</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>knärot16, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>568267</v>
+        <v>568149</v>
       </c>
       <c r="R36" t="n">
-        <v>6399069</v>
+        <v>6398945</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4563,22 +4563,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123949221</v>
+        <v>123953876</v>
       </c>
       <c r="B37" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4587,49 +4587,52 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Knärot5, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>568277</v>
+        <v>568313</v>
       </c>
       <c r="R37" t="n">
-        <v>6399002</v>
+        <v>6399116</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4674,22 +4677,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123953876</v>
+        <v>123953963</v>
       </c>
       <c r="B38" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4698,38 +4701,35 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4737,10 +4737,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>568313</v>
+        <v>568310</v>
       </c>
       <c r="R38" t="n">
-        <v>6399116</v>
+        <v>6399096</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4800,7 +4800,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123953963</v>
+        <v>123949221</v>
       </c>
       <c r="B39" t="n">
         <v>98079</v>
@@ -4833,28 +4833,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>Knärot5, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>568310</v>
+        <v>568277</v>
       </c>
       <c r="R39" t="n">
-        <v>6399096</v>
+        <v>6399002</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4899,12 +4899,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5244,7 +5244,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123953775</v>
+        <v>123949558</v>
       </c>
       <c r="B43" t="n">
         <v>98079</v>
@@ -5277,28 +5277,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot17, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>568273</v>
+        <v>568320</v>
       </c>
       <c r="R43" t="n">
-        <v>6399048</v>
+        <v>6399077</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5343,19 +5343,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123953988</v>
+        <v>123949415</v>
       </c>
       <c r="B44" t="n">
         <v>98079</v>
@@ -5388,28 +5388,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot12, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>568342</v>
+        <v>568329</v>
       </c>
       <c r="R44" t="n">
-        <v>6399127</v>
+        <v>6399041</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5454,19 +5454,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123949558</v>
+        <v>123953775</v>
       </c>
       <c r="B45" t="n">
         <v>98079</v>
@@ -5499,28 +5499,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>knärot17, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>568320</v>
+        <v>568273</v>
       </c>
       <c r="R45" t="n">
-        <v>6399077</v>
+        <v>6399048</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5565,19 +5565,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123949415</v>
+        <v>123953988</v>
       </c>
       <c r="B46" t="n">
         <v>98079</v>
@@ -5610,28 +5610,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>knärot12, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>568329</v>
+        <v>568342</v>
       </c>
       <c r="R46" t="n">
-        <v>6399041</v>
+        <v>6399127</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5676,12 +5676,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>

--- a/artfynd/A 16004-2025 artfynd.xlsx
+++ b/artfynd/A 16004-2025 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123842053</v>
+        <v>123842561</v>
       </c>
       <c r="B3" t="n">
         <v>98079</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -830,17 +830,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Knärot1, Sm</t>
+          <t>Knärot3, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568157</v>
+        <v>568178</v>
       </c>
       <c r="R3" t="n">
-        <v>6398918</v>
+        <v>6398997</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123842561</v>
+        <v>123842288</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -941,17 +941,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Knärot3, Sm</t>
+          <t>Knärot2, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568178</v>
+        <v>568186</v>
       </c>
       <c r="R4" t="n">
-        <v>6398997</v>
+        <v>6398957</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123842288</v>
+        <v>123842053</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1052,14 +1052,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Knärot2, Sm</t>
+          <t>Knärot1, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568186</v>
+        <v>568157</v>
       </c>
       <c r="R5" t="n">
-        <v>6398957</v>
+        <v>6398918</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123875253</v>
+        <v>123875271</v>
       </c>
       <c r="B7" t="n">
-        <v>90426</v>
+        <v>57507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,34 +1246,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2008</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1325,7 +1326,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1344,7 +1344,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123875158</v>
+        <v>123875073</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568173</v>
+        <v>568169</v>
       </c>
       <c r="R8" t="n">
-        <v>6398964</v>
+        <v>6398913</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123875178</v>
+        <v>123875103</v>
       </c>
       <c r="B9" t="n">
-        <v>57644</v>
+        <v>57507</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,33 +1471,29 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1507,13 +1503,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568147</v>
+        <v>568178</v>
       </c>
       <c r="R9" t="n">
-        <v>6398938</v>
+        <v>6398985</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1543,6 +1539,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Bearbetat stubbe</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,7 +1570,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123875073</v>
+        <v>123875213</v>
       </c>
       <c r="B10" t="n">
         <v>98079</v>
@@ -1617,10 +1618,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568169</v>
+        <v>568121</v>
       </c>
       <c r="R10" t="n">
-        <v>6398913</v>
+        <v>6398922</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,10 +1681,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123875103</v>
+        <v>123875178</v>
       </c>
       <c r="B11" t="n">
-        <v>57507</v>
+        <v>57644</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1696,29 +1697,33 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1728,13 +1733,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568178</v>
+        <v>568147</v>
       </c>
       <c r="R11" t="n">
-        <v>6398985</v>
+        <v>6398938</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1764,11 +1769,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Bearbetat stubbe</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,7 +1795,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123875213</v>
+        <v>123875158</v>
       </c>
       <c r="B12" t="n">
         <v>98079</v>
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568121</v>
+        <v>568173</v>
       </c>
       <c r="R12" t="n">
-        <v>6398922</v>
+        <v>6398964</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1906,10 +1906,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123875271</v>
+        <v>123875253</v>
       </c>
       <c r="B13" t="n">
-        <v>57507</v>
+        <v>90426</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1922,35 +1922,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>2008</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2002,6 +2001,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2020,7 +2020,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123953814</v>
+        <v>123949545</v>
       </c>
       <c r="B14" t="n">
         <v>98079</v>
@@ -2053,28 +2053,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot16, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>568298</v>
+        <v>568267</v>
       </c>
       <c r="R14" t="n">
-        <v>6399059</v>
+        <v>6399069</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123949240</v>
+        <v>123953122</v>
       </c>
       <c r="B15" t="n">
-        <v>98079</v>
+        <v>90426</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2143,49 +2143,52 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>2008</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>knärot6, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>568285</v>
+        <v>568149</v>
       </c>
       <c r="R15" t="n">
-        <v>6399024</v>
+        <v>6398945</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2230,19 +2233,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123954009</v>
+        <v>123953665</v>
       </c>
       <c r="B16" t="n">
         <v>98079</v>
@@ -2290,10 +2293,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>568399</v>
+        <v>568251</v>
       </c>
       <c r="R16" t="n">
-        <v>6399091</v>
+        <v>6399046</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2346,14 +2349,14 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123949273</v>
+        <v>123953775</v>
       </c>
       <c r="B17" t="n">
         <v>98079</v>
@@ -2386,28 +2389,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>knärot9, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>568260</v>
+        <v>568273</v>
       </c>
       <c r="R17" t="n">
-        <v>6399040</v>
+        <v>6399048</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2452,19 +2455,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123953938</v>
+        <v>123949584</v>
       </c>
       <c r="B18" t="n">
         <v>98079</v>
@@ -2497,28 +2500,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot20, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>568321</v>
+        <v>568393</v>
       </c>
       <c r="R18" t="n">
-        <v>6399110</v>
+        <v>6399083</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2563,7 +2566,7 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -2575,10 +2578,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123953317</v>
+        <v>123954300</v>
       </c>
       <c r="B19" t="n">
-        <v>98079</v>
+        <v>56700</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2587,46 +2590,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>A 16004, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>568247</v>
+        <v>568340</v>
       </c>
       <c r="R19" t="n">
-        <v>6399025</v>
+        <v>6399053</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2661,13 +2668,17 @@
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Flera fjödrar ovh dun.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2686,7 +2697,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123953357</v>
+        <v>123949592</v>
       </c>
       <c r="B20" t="n">
         <v>98079</v>
@@ -2719,28 +2730,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot21, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>568247</v>
+        <v>568397</v>
       </c>
       <c r="R20" t="n">
-        <v>6399016</v>
+        <v>6399096</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2785,7 +2796,7 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -2797,7 +2808,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123953575</v>
+        <v>123953963</v>
       </c>
       <c r="B21" t="n">
         <v>98079</v>
@@ -2845,10 +2856,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>568284</v>
+        <v>568310</v>
       </c>
       <c r="R21" t="n">
-        <v>6399026</v>
+        <v>6399096</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2908,7 +2919,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123953289</v>
+        <v>123949415</v>
       </c>
       <c r="B22" t="n">
         <v>98079</v>
@@ -2941,28 +2952,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot12, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>568244</v>
+        <v>568329</v>
       </c>
       <c r="R22" t="n">
-        <v>6399023</v>
+        <v>6399041</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3007,19 +3018,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123949592</v>
+        <v>123953836</v>
       </c>
       <c r="B23" t="n">
         <v>98079</v>
@@ -3052,28 +3063,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>knärot21, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>568397</v>
+        <v>568294</v>
       </c>
       <c r="R23" t="n">
-        <v>6399096</v>
+        <v>6399059</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3118,12 +3129,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3241,10 +3252,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123954151</v>
+        <v>123953938</v>
       </c>
       <c r="B25" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3253,35 +3264,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3289,10 +3300,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>568376</v>
+        <v>568321</v>
       </c>
       <c r="R25" t="n">
-        <v>6399112</v>
+        <v>6399110</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3333,6 +3344,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3351,7 +3363,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123954103</v>
+        <v>123953735</v>
       </c>
       <c r="B26" t="n">
         <v>98079</v>
@@ -3399,10 +3411,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>568389</v>
+        <v>568269</v>
       </c>
       <c r="R26" t="n">
-        <v>6399101</v>
+        <v>6399049</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3455,17 +3467,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123953913</v>
+        <v>123949558</v>
       </c>
       <c r="B27" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3474,49 +3486,49 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot17, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>568321</v>
+        <v>568320</v>
       </c>
       <c r="R27" t="n">
-        <v>6399110</v>
+        <v>6399077</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3561,7 +3573,7 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
@@ -3573,10 +3585,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123949584</v>
+        <v>123953648</v>
       </c>
       <c r="B28" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3585,49 +3597,49 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>knärot20, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>568393</v>
+        <v>568268</v>
       </c>
       <c r="R28" t="n">
-        <v>6399083</v>
+        <v>6399043</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3665,26 +3677,25 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123953590</v>
+        <v>123949566</v>
       </c>
       <c r="B29" t="n">
         <v>98079</v>
@@ -3717,28 +3728,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot18, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>568287</v>
+        <v>568308</v>
       </c>
       <c r="R29" t="n">
-        <v>6399029</v>
+        <v>6399081</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3783,7 +3794,7 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
@@ -3795,7 +3806,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123953616</v>
+        <v>123954103</v>
       </c>
       <c r="B30" t="n">
         <v>98079</v>
@@ -3843,10 +3854,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>568263</v>
+        <v>568389</v>
       </c>
       <c r="R30" t="n">
-        <v>6399041</v>
+        <v>6399101</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3899,14 +3910,14 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123949397</v>
+        <v>123953227</v>
       </c>
       <c r="B31" t="n">
         <v>98079</v>
@@ -3939,28 +3950,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>knärot11, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>568292</v>
+        <v>568237</v>
       </c>
       <c r="R31" t="n">
-        <v>6399045</v>
+        <v>6399031</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4005,19 +4016,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123949609</v>
+        <v>123949261</v>
       </c>
       <c r="B32" t="n">
         <v>98079</v>
@@ -4052,7 +4063,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -4061,14 +4072,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>knärot21, Sm</t>
+          <t>knärot8, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>568313</v>
+        <v>568271</v>
       </c>
       <c r="R32" t="n">
-        <v>6399119</v>
+        <v>6399036</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4128,7 +4139,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123953533</v>
+        <v>123949249</v>
       </c>
       <c r="B33" t="n">
         <v>98079</v>
@@ -4161,28 +4172,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot7, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
         <v>568291</v>
       </c>
       <c r="R33" t="n">
-        <v>6398999</v>
+        <v>6399043</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4227,19 +4238,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123953836</v>
+        <v>123954009</v>
       </c>
       <c r="B34" t="n">
         <v>98079</v>
@@ -4287,10 +4298,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>568294</v>
+        <v>568399</v>
       </c>
       <c r="R34" t="n">
-        <v>6399059</v>
+        <v>6399091</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4343,14 +4354,14 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123949545</v>
+        <v>123953317</v>
       </c>
       <c r="B35" t="n">
         <v>98079</v>
@@ -4383,28 +4394,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>knärot16, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>568267</v>
+        <v>568247</v>
       </c>
       <c r="R35" t="n">
-        <v>6399069</v>
+        <v>6399025</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4449,22 +4460,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123953122</v>
+        <v>123953616</v>
       </c>
       <c r="B36" t="n">
-        <v>90426</v>
+        <v>98079</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4473,38 +4484,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2008</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4512,10 +4520,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>568149</v>
+        <v>568263</v>
       </c>
       <c r="R36" t="n">
-        <v>6398945</v>
+        <v>6399041</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4575,10 +4583,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123953876</v>
+        <v>123953575</v>
       </c>
       <c r="B37" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4587,38 +4595,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4626,10 +4631,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>568313</v>
+        <v>568284</v>
       </c>
       <c r="R37" t="n">
-        <v>6399116</v>
+        <v>6399026</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4689,10 +4694,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123953963</v>
+        <v>123954151</v>
       </c>
       <c r="B38" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4701,35 +4706,35 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4737,10 +4742,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>568310</v>
+        <v>568376</v>
       </c>
       <c r="R38" t="n">
-        <v>6399096</v>
+        <v>6399112</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4781,7 +4786,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4800,7 +4804,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123949221</v>
+        <v>123953683</v>
       </c>
       <c r="B39" t="n">
         <v>98079</v>
@@ -4833,28 +4837,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Knärot5, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>568277</v>
+        <v>568248</v>
       </c>
       <c r="R39" t="n">
-        <v>6399002</v>
+        <v>6399053</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4899,19 +4899,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123953794</v>
+        <v>123953988</v>
       </c>
       <c r="B40" t="n">
         <v>98079</v>
@@ -4959,10 +4959,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>568305</v>
+        <v>568342</v>
       </c>
       <c r="R40" t="n">
-        <v>6399047</v>
+        <v>6399127</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5022,7 +5022,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123949261</v>
+        <v>123953509</v>
       </c>
       <c r="B41" t="n">
         <v>98079</v>
@@ -5055,28 +5055,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>knärot8, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>568271</v>
+        <v>568275</v>
       </c>
       <c r="R41" t="n">
-        <v>6399036</v>
+        <v>6399010</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5121,19 +5121,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123949298</v>
+        <v>123953814</v>
       </c>
       <c r="B42" t="n">
         <v>98079</v>
@@ -5166,28 +5166,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>knärot10, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>568243</v>
+        <v>568298</v>
       </c>
       <c r="R42" t="n">
-        <v>6399034</v>
+        <v>6399059</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5232,19 +5232,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123949558</v>
+        <v>123953467</v>
       </c>
       <c r="B43" t="n">
         <v>98079</v>
@@ -5277,28 +5277,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>knärot17, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>568320</v>
+        <v>568277</v>
       </c>
       <c r="R43" t="n">
-        <v>6399077</v>
+        <v>6399026</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
@@ -5355,7 +5355,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123949415</v>
+        <v>123949221</v>
       </c>
       <c r="B44" t="n">
         <v>98079</v>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
@@ -5399,14 +5399,14 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>knärot12, Sm</t>
+          <t>Knärot5, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>568329</v>
+        <v>568277</v>
       </c>
       <c r="R44" t="n">
-        <v>6399041</v>
+        <v>6399002</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5466,7 +5466,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123953775</v>
+        <v>123949609</v>
       </c>
       <c r="B45" t="n">
         <v>98079</v>
@@ -5499,28 +5499,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot21, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>568273</v>
+        <v>568313</v>
       </c>
       <c r="R45" t="n">
-        <v>6399048</v>
+        <v>6399119</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
@@ -5577,7 +5577,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123953988</v>
+        <v>123949397</v>
       </c>
       <c r="B46" t="n">
         <v>98079</v>
@@ -5610,28 +5610,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot11, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>568342</v>
+        <v>568292</v>
       </c>
       <c r="R46" t="n">
-        <v>6399127</v>
+        <v>6399045</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5676,22 +5676,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123954184</v>
+        <v>123953876</v>
       </c>
       <c r="B47" t="n">
-        <v>57507</v>
+        <v>90990</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5704,31 +5704,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5736,10 +5739,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>568372</v>
+        <v>568313</v>
       </c>
       <c r="R47" t="n">
-        <v>6399087</v>
+        <v>6399116</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5780,6 +5783,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5798,7 +5802,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123953185</v>
+        <v>123949240</v>
       </c>
       <c r="B48" t="n">
         <v>98079</v>
@@ -5831,28 +5835,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot6, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>568156</v>
+        <v>568285</v>
       </c>
       <c r="R48" t="n">
-        <v>6398944</v>
+        <v>6399024</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5897,22 +5901,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123953735</v>
+        <v>123953913</v>
       </c>
       <c r="B49" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5921,25 +5925,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5957,10 +5961,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>568269</v>
+        <v>568321</v>
       </c>
       <c r="R49" t="n">
-        <v>6399049</v>
+        <v>6399110</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6020,10 +6024,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123954300</v>
+        <v>123953533</v>
       </c>
       <c r="B50" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6032,50 +6036,46 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>funnen död</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>A 16004, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>568340</v>
+        <v>568291</v>
       </c>
       <c r="R50" t="n">
-        <v>6399053</v>
+        <v>6398999</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6110,17 +6110,13 @@
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Flera fjödrar ovh dun.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6139,7 +6135,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123949249</v>
+        <v>123953185</v>
       </c>
       <c r="B51" t="n">
         <v>98079</v>
@@ -6172,28 +6168,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>knärot7, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>568291</v>
+        <v>568156</v>
       </c>
       <c r="R51" t="n">
-        <v>6399043</v>
+        <v>6398944</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6238,22 +6234,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123953683</v>
+        <v>123954184</v>
       </c>
       <c r="B52" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6262,31 +6258,35 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6294,10 +6294,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>568248</v>
+        <v>568372</v>
       </c>
       <c r="R52" t="n">
-        <v>6399053</v>
+        <v>6399087</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6338,7 +6338,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6357,7 +6356,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123953665</v>
+        <v>123949577</v>
       </c>
       <c r="B53" t="n">
         <v>98079</v>
@@ -6390,28 +6389,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot19, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>568251</v>
+        <v>568383</v>
       </c>
       <c r="R53" t="n">
-        <v>6399046</v>
+        <v>6399086</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6456,7 +6455,7 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
@@ -6468,7 +6467,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123953509</v>
+        <v>123949273</v>
       </c>
       <c r="B54" t="n">
         <v>98079</v>
@@ -6501,28 +6500,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot9, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>568275</v>
+        <v>568260</v>
       </c>
       <c r="R54" t="n">
-        <v>6399010</v>
+        <v>6399040</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6567,19 +6566,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123953467</v>
+        <v>123949298</v>
       </c>
       <c r="B55" t="n">
         <v>98079</v>
@@ -6612,28 +6611,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot10, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>568277</v>
+        <v>568243</v>
       </c>
       <c r="R55" t="n">
-        <v>6399026</v>
+        <v>6399034</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6678,7 +6677,7 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
@@ -6690,7 +6689,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123949577</v>
+        <v>123953357</v>
       </c>
       <c r="B56" t="n">
         <v>98079</v>
@@ -6723,28 +6722,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>knärot19, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>568383</v>
+        <v>568247</v>
       </c>
       <c r="R56" t="n">
-        <v>6399086</v>
+        <v>6399016</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6789,19 +6788,19 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123953227</v>
+        <v>123953590</v>
       </c>
       <c r="B57" t="n">
         <v>98079</v>
@@ -6849,10 +6848,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>568237</v>
+        <v>568287</v>
       </c>
       <c r="R57" t="n">
-        <v>6399031</v>
+        <v>6399029</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6912,7 +6911,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123949566</v>
+        <v>123953794</v>
       </c>
       <c r="B58" t="n">
         <v>98079</v>
@@ -6945,28 +6944,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>knärot18, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>568308</v>
+        <v>568305</v>
       </c>
       <c r="R58" t="n">
-        <v>6399081</v>
+        <v>6399047</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7011,22 +7010,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123953648</v>
+        <v>123953289</v>
       </c>
       <c r="B59" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7035,35 +7034,35 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7071,13 +7070,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>568268</v>
+        <v>568244</v>
       </c>
       <c r="R59" t="n">
-        <v>6399043</v>
+        <v>6399023</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7115,6 +7114,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7133,10 +7133,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123978510</v>
+        <v>123978490</v>
       </c>
       <c r="B60" t="n">
-        <v>57861</v>
+        <v>96957</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7149,35 +7149,35 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7185,13 +7185,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>568326</v>
+        <v>568355</v>
       </c>
       <c r="R60" t="n">
-        <v>6399091</v>
+        <v>6399066</v>
       </c>
       <c r="S60" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7229,6 +7229,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7247,10 +7248,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123978490</v>
+        <v>123978510</v>
       </c>
       <c r="B61" t="n">
-        <v>96957</v>
+        <v>57861</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7263,35 +7264,35 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7299,13 +7300,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>568355</v>
+        <v>568326</v>
       </c>
       <c r="R61" t="n">
-        <v>6399066</v>
+        <v>6399091</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7343,7 +7344,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16004-2025 artfynd.xlsx
+++ b/artfynd/A 16004-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123842779</v>
+        <v>123842053</v>
       </c>
       <c r="B2" t="n">
         <v>98079</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -719,17 +719,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Knärot4, Sm</t>
+          <t>Knärot1, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568160</v>
+        <v>568157</v>
       </c>
       <c r="R2" t="n">
-        <v>6398949</v>
+        <v>6398918</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123842561</v>
+        <v>123842779</v>
       </c>
       <c r="B3" t="n">
         <v>98079</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -830,14 +830,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Knärot3, Sm</t>
+          <t>Knärot4, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568178</v>
+        <v>568160</v>
       </c>
       <c r="R3" t="n">
-        <v>6398997</v>
+        <v>6398949</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -890,14 +890,14 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123842288</v>
+        <v>123842561</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -941,17 +941,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Knärot2, Sm</t>
+          <t>Knärot3, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568186</v>
+        <v>568178</v>
       </c>
       <c r="R4" t="n">
-        <v>6398957</v>
+        <v>6398997</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123842053</v>
+        <v>123842288</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1052,14 +1052,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Knärot1, Sm</t>
+          <t>Knärot2, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568157</v>
+        <v>568186</v>
       </c>
       <c r="R5" t="n">
-        <v>6398918</v>
+        <v>6398957</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123875130</v>
+        <v>123875158</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568185</v>
+        <v>568173</v>
       </c>
       <c r="R6" t="n">
-        <v>6398991</v>
+        <v>6398964</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123875271</v>
+        <v>123875103</v>
       </c>
       <c r="B7" t="n">
         <v>57507</v>
@@ -1263,16 +1263,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1282,13 +1278,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568147</v>
+        <v>568178</v>
       </c>
       <c r="R7" t="n">
-        <v>6398938</v>
+        <v>6398985</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1318,6 +1314,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Bearbetat stubbe</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,7 +1345,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123875073</v>
+        <v>123875213</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1392,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568169</v>
+        <v>568121</v>
       </c>
       <c r="R8" t="n">
-        <v>6398913</v>
+        <v>6398922</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,10 +1456,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123875103</v>
+        <v>123875130</v>
       </c>
       <c r="B9" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,35 +1468,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1503,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568178</v>
+        <v>568185</v>
       </c>
       <c r="R9" t="n">
-        <v>6398985</v>
+        <v>6398991</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,17 +1542,13 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Bearbetat stubbe</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1570,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123875213</v>
+        <v>123875271</v>
       </c>
       <c r="B10" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1582,35 +1579,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1618,13 +1619,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568121</v>
+        <v>568147</v>
       </c>
       <c r="R10" t="n">
-        <v>6398922</v>
+        <v>6398938</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1662,7 +1663,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1681,10 +1681,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123875178</v>
+        <v>123875253</v>
       </c>
       <c r="B11" t="n">
-        <v>57644</v>
+        <v>90426</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1697,35 +1697,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>2008</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1777,6 +1776,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123875158</v>
+        <v>123875178</v>
       </c>
       <c r="B12" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,35 +1807,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1843,13 +1847,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>568173</v>
+        <v>568147</v>
       </c>
       <c r="R12" t="n">
-        <v>6398964</v>
+        <v>6398938</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1887,7 +1891,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1906,10 +1909,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123875253</v>
+        <v>123875073</v>
       </c>
       <c r="B13" t="n">
-        <v>90426</v>
+        <v>98079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1918,38 +1921,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2008</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1957,13 +1957,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>568147</v>
+        <v>568169</v>
       </c>
       <c r="R13" t="n">
-        <v>6398938</v>
+        <v>6398913</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123954103</v>
+        <v>123953227</v>
       </c>
       <c r="B30" t="n">
         <v>98079</v>
@@ -3854,10 +3854,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>568389</v>
+        <v>568237</v>
       </c>
       <c r="R30" t="n">
-        <v>6399101</v>
+        <v>6399031</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3910,14 +3910,14 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123953227</v>
+        <v>123954103</v>
       </c>
       <c r="B31" t="n">
         <v>98079</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>568237</v>
+        <v>568389</v>
       </c>
       <c r="R31" t="n">
-        <v>6399031</v>
+        <v>6399101</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4694,10 +4694,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123954151</v>
+        <v>123949221</v>
       </c>
       <c r="B38" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4706,49 +4706,49 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>Knärot5, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>568376</v>
+        <v>568277</v>
       </c>
       <c r="R38" t="n">
-        <v>6399112</v>
+        <v>6399002</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4786,25 +4786,26 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123953683</v>
+        <v>123949609</v>
       </c>
       <c r="B39" t="n">
         <v>98079</v>
@@ -4837,24 +4838,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot21, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>568248</v>
+        <v>568313</v>
       </c>
       <c r="R39" t="n">
-        <v>6399053</v>
+        <v>6399119</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4899,7 +4904,7 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
@@ -4911,10 +4916,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123953988</v>
+        <v>123954151</v>
       </c>
       <c r="B40" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4923,35 +4928,35 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4959,10 +4964,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>568342</v>
+        <v>568376</v>
       </c>
       <c r="R40" t="n">
-        <v>6399127</v>
+        <v>6399112</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5003,7 +5008,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5022,7 +5026,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123953509</v>
+        <v>123953683</v>
       </c>
       <c r="B41" t="n">
         <v>98079</v>
@@ -5056,11 +5060,7 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
@@ -5070,10 +5070,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>568275</v>
+        <v>568248</v>
       </c>
       <c r="R41" t="n">
-        <v>6399010</v>
+        <v>6399053</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5133,7 +5133,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123953814</v>
+        <v>123953988</v>
       </c>
       <c r="B42" t="n">
         <v>98079</v>
@@ -5181,10 +5181,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>568298</v>
+        <v>568342</v>
       </c>
       <c r="R42" t="n">
-        <v>6399059</v>
+        <v>6399127</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5244,7 +5244,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123953467</v>
+        <v>123953509</v>
       </c>
       <c r="B43" t="n">
         <v>98079</v>
@@ -5292,10 +5292,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>568277</v>
+        <v>568275</v>
       </c>
       <c r="R43" t="n">
-        <v>6399026</v>
+        <v>6399010</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5348,14 +5348,14 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123949221</v>
+        <v>123953814</v>
       </c>
       <c r="B44" t="n">
         <v>98079</v>
@@ -5388,28 +5388,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Knärot5, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>568277</v>
+        <v>568298</v>
       </c>
       <c r="R44" t="n">
-        <v>6399002</v>
+        <v>6399059</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5454,19 +5454,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123949609</v>
+        <v>123953467</v>
       </c>
       <c r="B45" t="n">
         <v>98079</v>
@@ -5499,28 +5499,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>knärot21, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>568313</v>
+        <v>568277</v>
       </c>
       <c r="R45" t="n">
-        <v>6399119</v>
+        <v>6399026</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5565,12 +5565,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 16004-2025 artfynd.xlsx
+++ b/artfynd/A 16004-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123842053</v>
+        <v>123842561</v>
       </c>
       <c r="B2" t="n">
         <v>98079</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -719,17 +719,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Knärot1, Sm</t>
+          <t>Knärot3, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568157</v>
+        <v>568178</v>
       </c>
       <c r="R2" t="n">
-        <v>6398918</v>
+        <v>6398997</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123842779</v>
+        <v>123842053</v>
       </c>
       <c r="B3" t="n">
         <v>98079</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -830,17 +830,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Knärot4, Sm</t>
+          <t>Knärot1, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568160</v>
+        <v>568157</v>
       </c>
       <c r="R3" t="n">
-        <v>6398949</v>
+        <v>6398918</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,14 +890,14 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123842561</v>
+        <v>123842288</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -941,17 +941,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Knärot3, Sm</t>
+          <t>Knärot2, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568178</v>
+        <v>568186</v>
       </c>
       <c r="R4" t="n">
-        <v>6398997</v>
+        <v>6398957</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123842288</v>
+        <v>123842779</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1052,17 +1052,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Knärot2, Sm</t>
+          <t>Knärot4, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568186</v>
+        <v>568160</v>
       </c>
       <c r="R5" t="n">
-        <v>6398957</v>
+        <v>6398949</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123875158</v>
+        <v>123875130</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568173</v>
+        <v>568185</v>
       </c>
       <c r="R6" t="n">
-        <v>6398964</v>
+        <v>6398991</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123875103</v>
+        <v>123875271</v>
       </c>
       <c r="B7" t="n">
         <v>57507</v>
@@ -1263,12 +1263,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1278,13 +1282,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568178</v>
+        <v>568147</v>
       </c>
       <c r="R7" t="n">
-        <v>6398985</v>
+        <v>6398938</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,11 +1318,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Bearbetat stubbe</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123875213</v>
+        <v>123875103</v>
       </c>
       <c r="B8" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,35 +1356,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1393,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568121</v>
+        <v>568178</v>
       </c>
       <c r="R8" t="n">
-        <v>6398922</v>
+        <v>6398985</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,13 +1430,17 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Bearbetat stubbe</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1456,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123875130</v>
+        <v>123875073</v>
       </c>
       <c r="B9" t="n">
         <v>98079</v>
@@ -1504,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568185</v>
+        <v>568169</v>
       </c>
       <c r="R9" t="n">
-        <v>6398991</v>
+        <v>6398913</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,10 +1570,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123875271</v>
+        <v>123875213</v>
       </c>
       <c r="B10" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,39 +1582,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1619,13 +1618,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568147</v>
+        <v>568121</v>
       </c>
       <c r="R10" t="n">
-        <v>6398938</v>
+        <v>6398922</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1663,6 +1662,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1681,10 +1681,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123875253</v>
+        <v>123875158</v>
       </c>
       <c r="B11" t="n">
-        <v>90426</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1693,38 +1693,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2008</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1732,13 +1729,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568147</v>
+        <v>568173</v>
       </c>
       <c r="R11" t="n">
-        <v>6398938</v>
+        <v>6398964</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1795,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123875178</v>
+        <v>123875253</v>
       </c>
       <c r="B12" t="n">
-        <v>57644</v>
+        <v>90426</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,35 +1808,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>2008</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1891,6 +1887,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1909,10 +1906,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123875073</v>
+        <v>123875178</v>
       </c>
       <c r="B13" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1921,35 +1918,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1957,13 +1958,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>568169</v>
+        <v>568147</v>
       </c>
       <c r="R13" t="n">
-        <v>6398913</v>
+        <v>6398938</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2001,7 +2002,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2020,7 +2020,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123949545</v>
+        <v>123953794</v>
       </c>
       <c r="B14" t="n">
         <v>98079</v>
@@ -2053,28 +2053,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>knärot16, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>568267</v>
+        <v>568305</v>
       </c>
       <c r="R14" t="n">
-        <v>6399069</v>
+        <v>6399047</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2119,22 +2119,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123953122</v>
+        <v>123953509</v>
       </c>
       <c r="B15" t="n">
-        <v>90426</v>
+        <v>98079</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2143,38 +2143,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2008</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2182,10 +2179,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>568149</v>
+        <v>568275</v>
       </c>
       <c r="R15" t="n">
-        <v>6398945</v>
+        <v>6399010</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2238,14 +2235,14 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123953665</v>
+        <v>123954009</v>
       </c>
       <c r="B16" t="n">
         <v>98079</v>
@@ -2293,10 +2290,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>568251</v>
+        <v>568399</v>
       </c>
       <c r="R16" t="n">
-        <v>6399046</v>
+        <v>6399091</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2349,14 +2346,14 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123953775</v>
+        <v>123949221</v>
       </c>
       <c r="B17" t="n">
         <v>98079</v>
@@ -2389,28 +2386,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>Knärot5, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>568273</v>
+        <v>568277</v>
       </c>
       <c r="R17" t="n">
-        <v>6399048</v>
+        <v>6399002</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2455,7 +2452,7 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -2467,10 +2464,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123949584</v>
+        <v>123954151</v>
       </c>
       <c r="B18" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2479,49 +2476,49 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>knärot20, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>568393</v>
+        <v>568376</v>
       </c>
       <c r="R18" t="n">
-        <v>6399083</v>
+        <v>6399112</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2559,14 +2556,13 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -2578,10 +2574,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123954300</v>
+        <v>123949397</v>
       </c>
       <c r="B19" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2590,53 +2586,49 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>funnen död</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>A 16004, Sm</t>
+          <t>knärot11, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>568340</v>
+        <v>568292</v>
       </c>
       <c r="R19" t="n">
-        <v>6399053</v>
+        <v>6399045</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2668,39 +2660,35 @@
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Flera fjödrar ovh dun.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123949592</v>
+        <v>123954300</v>
       </c>
       <c r="B20" t="n">
-        <v>98079</v>
+        <v>56700</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2709,49 +2697,53 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>knärot21, Sm</t>
+          <t>A 16004, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>568397</v>
+        <v>568340</v>
       </c>
       <c r="R20" t="n">
-        <v>6399096</v>
+        <v>6399053</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2783,20 +2775,24 @@
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Flera fjödrar ovh dun.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -2808,7 +2804,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123953963</v>
+        <v>123954103</v>
       </c>
       <c r="B21" t="n">
         <v>98079</v>
@@ -2856,10 +2852,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>568310</v>
+        <v>568389</v>
       </c>
       <c r="R21" t="n">
-        <v>6399096</v>
+        <v>6399101</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2912,14 +2908,14 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123949415</v>
+        <v>123953289</v>
       </c>
       <c r="B22" t="n">
         <v>98079</v>
@@ -2952,28 +2948,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>knärot12, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>568329</v>
+        <v>568244</v>
       </c>
       <c r="R22" t="n">
-        <v>6399041</v>
+        <v>6399023</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3018,19 +3014,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123953836</v>
+        <v>123953963</v>
       </c>
       <c r="B23" t="n">
         <v>98079</v>
@@ -3078,10 +3074,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>568294</v>
+        <v>568310</v>
       </c>
       <c r="R23" t="n">
-        <v>6399059</v>
+        <v>6399096</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3141,7 +3137,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123953559</v>
+        <v>123953616</v>
       </c>
       <c r="B24" t="n">
         <v>98079</v>
@@ -3189,10 +3185,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>568271</v>
+        <v>568263</v>
       </c>
       <c r="R24" t="n">
-        <v>6399014</v>
+        <v>6399041</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3252,7 +3248,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123953938</v>
+        <v>123949577</v>
       </c>
       <c r="B25" t="n">
         <v>98079</v>
@@ -3285,28 +3281,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot19, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>568321</v>
+        <v>568383</v>
       </c>
       <c r="R25" t="n">
-        <v>6399110</v>
+        <v>6399086</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3351,19 +3347,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123953735</v>
+        <v>123949566</v>
       </c>
       <c r="B26" t="n">
         <v>98079</v>
@@ -3396,28 +3392,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot18, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>568269</v>
+        <v>568308</v>
       </c>
       <c r="R26" t="n">
-        <v>6399049</v>
+        <v>6399081</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3462,19 +3458,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123949558</v>
+        <v>123949545</v>
       </c>
       <c r="B27" t="n">
         <v>98079</v>
@@ -3509,7 +3505,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -3518,14 +3514,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>knärot17, Sm</t>
+          <t>knärot16, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>568320</v>
+        <v>568267</v>
       </c>
       <c r="R27" t="n">
-        <v>6399077</v>
+        <v>6399069</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3578,17 +3574,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123953648</v>
+        <v>123953559</v>
       </c>
       <c r="B28" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3597,35 +3593,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3633,13 +3629,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>568268</v>
+        <v>568271</v>
       </c>
       <c r="R28" t="n">
-        <v>6399043</v>
+        <v>6399014</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3677,6 +3673,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3688,14 +3685,14 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123949566</v>
+        <v>123953575</v>
       </c>
       <c r="B29" t="n">
         <v>98079</v>
@@ -3728,28 +3725,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>knärot18, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>568308</v>
+        <v>568284</v>
       </c>
       <c r="R29" t="n">
-        <v>6399081</v>
+        <v>6399026</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3794,19 +3791,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123953227</v>
+        <v>123953988</v>
       </c>
       <c r="B30" t="n">
         <v>98079</v>
@@ -3854,10 +3851,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>568237</v>
+        <v>568342</v>
       </c>
       <c r="R30" t="n">
-        <v>6399031</v>
+        <v>6399127</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3917,7 +3914,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123954103</v>
+        <v>123953533</v>
       </c>
       <c r="B31" t="n">
         <v>98079</v>
@@ -3965,10 +3962,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>568389</v>
+        <v>568291</v>
       </c>
       <c r="R31" t="n">
-        <v>6399101</v>
+        <v>6398999</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4028,7 +4025,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123949261</v>
+        <v>123949592</v>
       </c>
       <c r="B32" t="n">
         <v>98079</v>
@@ -4063,7 +4060,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -4072,14 +4069,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>knärot8, Sm</t>
+          <t>knärot21, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>568271</v>
+        <v>568397</v>
       </c>
       <c r="R32" t="n">
-        <v>6399036</v>
+        <v>6399096</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4139,7 +4136,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123949249</v>
+        <v>123953836</v>
       </c>
       <c r="B33" t="n">
         <v>98079</v>
@@ -4172,28 +4169,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>knärot7, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>568291</v>
+        <v>568294</v>
       </c>
       <c r="R33" t="n">
-        <v>6399043</v>
+        <v>6399059</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4238,19 +4235,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123954009</v>
+        <v>123953590</v>
       </c>
       <c r="B34" t="n">
         <v>98079</v>
@@ -4298,10 +4295,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>568399</v>
+        <v>568287</v>
       </c>
       <c r="R34" t="n">
-        <v>6399091</v>
+        <v>6399029</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4361,7 +4358,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123953317</v>
+        <v>123953227</v>
       </c>
       <c r="B35" t="n">
         <v>98079</v>
@@ -4409,10 +4406,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>568247</v>
+        <v>568237</v>
       </c>
       <c r="R35" t="n">
-        <v>6399025</v>
+        <v>6399031</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4465,14 +4462,14 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123953616</v>
+        <v>123949584</v>
       </c>
       <c r="B36" t="n">
         <v>98079</v>
@@ -4505,28 +4502,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot20, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>568263</v>
+        <v>568393</v>
       </c>
       <c r="R36" t="n">
-        <v>6399041</v>
+        <v>6399083</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4571,19 +4568,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123953575</v>
+        <v>123949415</v>
       </c>
       <c r="B37" t="n">
         <v>98079</v>
@@ -4616,28 +4613,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot12, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>568284</v>
+        <v>568329</v>
       </c>
       <c r="R37" t="n">
-        <v>6399026</v>
+        <v>6399041</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4682,22 +4679,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123949221</v>
+        <v>123953648</v>
       </c>
       <c r="B38" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4706,49 +4703,49 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Knärot5, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>568277</v>
+        <v>568268</v>
       </c>
       <c r="R38" t="n">
-        <v>6399002</v>
+        <v>6399043</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4786,29 +4783,28 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123949609</v>
+        <v>123953876</v>
       </c>
       <c r="B39" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4817,49 +4813,52 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>knärot21, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
         <v>568313</v>
       </c>
       <c r="R39" t="n">
-        <v>6399119</v>
+        <v>6399116</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4904,7 +4903,7 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
@@ -4916,10 +4915,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123954151</v>
+        <v>123953938</v>
       </c>
       <c r="B40" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4928,35 +4927,35 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4964,10 +4963,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>568376</v>
+        <v>568321</v>
       </c>
       <c r="R40" t="n">
-        <v>6399112</v>
+        <v>6399110</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5008,6 +5007,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5026,7 +5026,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123953683</v>
+        <v>123953735</v>
       </c>
       <c r="B41" t="n">
         <v>98079</v>
@@ -5060,7 +5060,11 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
@@ -5070,10 +5074,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>568248</v>
+        <v>568269</v>
       </c>
       <c r="R41" t="n">
-        <v>6399053</v>
+        <v>6399049</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5126,14 +5130,14 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123953988</v>
+        <v>123953665</v>
       </c>
       <c r="B42" t="n">
         <v>98079</v>
@@ -5181,10 +5185,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>568342</v>
+        <v>568251</v>
       </c>
       <c r="R42" t="n">
-        <v>6399127</v>
+        <v>6399046</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5244,7 +5248,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123953509</v>
+        <v>123949609</v>
       </c>
       <c r="B43" t="n">
         <v>98079</v>
@@ -5277,28 +5281,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot21, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>568275</v>
+        <v>568313</v>
       </c>
       <c r="R43" t="n">
-        <v>6399010</v>
+        <v>6399119</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5343,22 +5347,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123953814</v>
+        <v>123953122</v>
       </c>
       <c r="B44" t="n">
-        <v>98079</v>
+        <v>90426</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5367,35 +5371,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>2008</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5403,10 +5410,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>568298</v>
+        <v>568149</v>
       </c>
       <c r="R44" t="n">
-        <v>6399059</v>
+        <v>6398945</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5466,10 +5473,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123953467</v>
+        <v>123954184</v>
       </c>
       <c r="B45" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5478,35 +5485,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5514,10 +5521,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>568277</v>
+        <v>568372</v>
       </c>
       <c r="R45" t="n">
-        <v>6399026</v>
+        <v>6399087</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5558,7 +5565,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5570,14 +5576,14 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123949397</v>
+        <v>123949261</v>
       </c>
       <c r="B46" t="n">
         <v>98079</v>
@@ -5612,7 +5618,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -5621,14 +5627,14 @@
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>knärot11, Sm</t>
+          <t>knärot8, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>568292</v>
+        <v>568271</v>
       </c>
       <c r="R46" t="n">
-        <v>6399045</v>
+        <v>6399036</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5681,17 +5687,17 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123953876</v>
+        <v>123949240</v>
       </c>
       <c r="B47" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5700,52 +5706,49 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot6, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>568313</v>
+        <v>568285</v>
       </c>
       <c r="R47" t="n">
-        <v>6399116</v>
+        <v>6399024</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5790,7 +5793,7 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
@@ -5802,7 +5805,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123949240</v>
+        <v>123949249</v>
       </c>
       <c r="B48" t="n">
         <v>98079</v>
@@ -5837,7 +5840,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -5846,14 +5849,14 @@
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>knärot6, Sm</t>
+          <t>knärot7, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>568285</v>
+        <v>568291</v>
       </c>
       <c r="R48" t="n">
-        <v>6399024</v>
+        <v>6399043</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5906,17 +5909,17 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123953913</v>
+        <v>123953185</v>
       </c>
       <c r="B49" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5925,25 +5928,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5961,10 +5964,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>568321</v>
+        <v>568156</v>
       </c>
       <c r="R49" t="n">
-        <v>6399110</v>
+        <v>6398944</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6017,14 +6020,14 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123953533</v>
+        <v>123953814</v>
       </c>
       <c r="B50" t="n">
         <v>98079</v>
@@ -6072,10 +6075,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>568291</v>
+        <v>568298</v>
       </c>
       <c r="R50" t="n">
-        <v>6398999</v>
+        <v>6399059</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6135,7 +6138,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123953185</v>
+        <v>123949558</v>
       </c>
       <c r="B51" t="n">
         <v>98079</v>
@@ -6168,28 +6171,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot17, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>568156</v>
+        <v>568320</v>
       </c>
       <c r="R51" t="n">
-        <v>6398944</v>
+        <v>6399077</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6234,22 +6237,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123954184</v>
+        <v>123949298</v>
       </c>
       <c r="B52" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6258,49 +6261,49 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot10, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>568372</v>
+        <v>568243</v>
       </c>
       <c r="R52" t="n">
-        <v>6399087</v>
+        <v>6399034</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6338,13 +6341,14 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
@@ -6356,10 +6360,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123949577</v>
+        <v>123953913</v>
       </c>
       <c r="B53" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6368,49 +6372,49 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>knärot19, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>568383</v>
+        <v>568321</v>
       </c>
       <c r="R53" t="n">
-        <v>6399086</v>
+        <v>6399110</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6455,7 +6459,7 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
@@ -6467,7 +6471,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123949273</v>
+        <v>123953467</v>
       </c>
       <c r="B54" t="n">
         <v>98079</v>
@@ -6500,28 +6504,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>knärot9, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>568260</v>
+        <v>568277</v>
       </c>
       <c r="R54" t="n">
-        <v>6399040</v>
+        <v>6399026</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6566,19 +6570,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anna Drenk, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Anna Drenk</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123949298</v>
+        <v>123953775</v>
       </c>
       <c r="B55" t="n">
         <v>98079</v>
@@ -6611,28 +6615,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>knärot10, Sm</t>
+          <t>A 16004, Ytterbo, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>568243</v>
+        <v>568273</v>
       </c>
       <c r="R55" t="n">
-        <v>6399034</v>
+        <v>6399048</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6677,7 +6681,7 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anna Drenk</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
@@ -6689,7 +6693,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123953357</v>
+        <v>123953683</v>
       </c>
       <c r="B56" t="n">
         <v>98079</v>
@@ -6723,11 +6727,7 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
@@ -6737,10 +6737,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>568247</v>
+        <v>568248</v>
       </c>
       <c r="R56" t="n">
-        <v>6399016</v>
+        <v>6399053</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6800,7 +6800,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123953590</v>
+        <v>123949273</v>
       </c>
       <c r="B57" t="n">
         <v>98079</v>
@@ -6833,28 +6833,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>A 16004, Ytterbo, Sm</t>
+          <t>knärot9, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>568287</v>
+        <v>568260</v>
       </c>
       <c r="R57" t="n">
-        <v>6399029</v>
+        <v>6399040</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Anna Drenk</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
@@ -6911,7 +6911,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123953794</v>
+        <v>123953317</v>
       </c>
       <c r="B58" t="n">
         <v>98079</v>
@@ -6959,10 +6959,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>568305</v>
+        <v>568247</v>
       </c>
       <c r="R58" t="n">
-        <v>6399047</v>
+        <v>6399025</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7022,7 +7022,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123953289</v>
+        <v>123953357</v>
       </c>
       <c r="B59" t="n">
         <v>98079</v>
@@ -7070,10 +7070,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>568244</v>
+        <v>568247</v>
       </c>
       <c r="R59" t="n">
-        <v>6399023</v>
+        <v>6399016</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7241,7 +7241,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Anna Drenk</t>
+          <t>Anna Drenk, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
